--- a/资料/资料目录.xlsx
+++ b/资料/资料目录.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资料目录" sheetId="1" r:id="R61c0094120134266"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资料目录" sheetId="1" r:id="Rdb34570a4b314faf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12,80 +12,88 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:styleSheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:numFmts count="1">
-    <ns0:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-  </ns0:numFmts>
-  <ns0:fonts count="3">
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:name val="Carlito"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:name val="等线"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:b/>
-      <ns0:sz val="11"/>
-      <ns0:name val="等线"/>
-    </ns0:font>
-  </ns0:fonts>
-  <ns0:fills count="3">
-    <ns0:fill>
-      <ns0:patternFill patternType="none"/>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="gray125"/>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="solid">
-        <ns0:fgColor rgb="FFFFFFFF"/>
-      </ns0:patternFill>
-    </ns0:fill>
-  </ns0:fills>
-  <ns0:borders count="1">
-    <ns0:border/>
-  </ns0:borders>
-  <ns0:cellStyleXfs count="1">
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </ns0:cellStyleXfs>
-  <ns0:cellXfs count="10">
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <ns0:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <ns0:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-  </ns0:cellXfs>
-  <ns0:cellStyles count="1">
-    <ns0:cellStyle name="Normal" xfId="0"/>
-  </ns0:cellStyles>
-</ns0:styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
+  <x:fonts count="3">
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="等线"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="等线"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="4">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border/>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="10">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
+  </x:cellStyles>
+</x:styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Library" displayName="Library" ref="A1:H26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Records1" displayName="Records1" ref="A1:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H33"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="手语歌（来源文件）"/>
     <x:tableColumn id="2" name="资料类型"/>
@@ -331,535 +339,680 @@
         <v>查看原件</v>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="8" t="str">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="4" t="str">
         <v>其实讲义editby二萌.docx</v>
       </c>
-      <c r="B2" s="8" t="str">
-        <v>手语歌讲义</v>
-      </c>
-      <c r="C2" s="9" t="n">
+      <c r="B2" s="4" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>45591</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="4" t="str">
         <v>小雪</v>
       </c>
-      <c r="E2" s="8" t="str">
+      <c r="E2" s="4" t="str">
         <v>二萌</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="8" t="n">
         <v>46019</v>
       </c>
-      <c r="G2" s="8" t="str">
+      <c r="G2" s="4" t="str">
         <v>授课日期列记录原稿日期</v>
       </c>
-      <c r="H2" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="8" t="str">
+      <c r="H2" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="5" t="str">
         <v>RE永远都会在 讲义 2.0ver (1).docx</v>
       </c>
-      <c r="B3" s="8" t="str">
+      <c r="B3" s="5" t="str">
         <v>手语歌讲义</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>45962</v>
       </c>
-      <c r="D3" s="8" t="str">
+      <c r="D3" s="5" t="str">
         <v>西柚、桃子</v>
       </c>
-      <c r="E3" s="8" t="str"/>
+      <c r="E3" s="5" t="str"/>
       <c r="F3" s="9" t="str"/>
-      <c r="G3" s="8" t="str">
+      <c r="G3" s="5" t="str">
         <v>讲义标注日期，授课或发布性质待确认</v>
       </c>
-      <c r="H3" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="8" t="str">
+      <c r="H3" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="str">
         <v>历历万乡.pdf</v>
       </c>
-      <c r="B4" s="8" t="str">
-        <v>手语歌讲义</v>
-      </c>
-      <c r="C4" s="9" t="n">
+      <c r="B4" s="4" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>45983</v>
       </c>
-      <c r="D4" s="8" t="str">
+      <c r="D4" s="4" t="str">
         <v>二萌</v>
       </c>
-      <c r="E4" s="8" t="str"/>
-      <c r="F4" s="9" t="str"/>
-      <c r="G4" s="8" t="str">
+      <c r="E4" s="4" t="str"/>
+      <c r="F4" s="8" t="str"/>
+      <c r="G4" s="4" t="str">
         <v>日期据讲义署名</v>
       </c>
-      <c r="H4" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="8" t="str">
+      <c r="H4" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="5" t="str">
         <v>海阔天空.docx</v>
       </c>
-      <c r="B5" s="8" t="str">
+      <c r="B5" s="5" t="str">
         <v>手语歌讲义</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>45993</v>
       </c>
-      <c r="D5" s="8" t="str">
+      <c r="D5" s="5" t="str">
         <v>大鱼、云杉</v>
       </c>
-      <c r="E5" s="8" t="str"/>
+      <c r="E5" s="5" t="str"/>
       <c r="F5" s="9" t="str"/>
-      <c r="G5" s="8" t="str">
+      <c r="G5" s="5" t="str">
         <v>日期为已确认授课日</v>
       </c>
-      <c r="H5" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="8" t="str">
+      <c r="H5" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="4" t="str">
         <v>光辉岁月讲义 (1).docx</v>
       </c>
-      <c r="B6" s="8" t="str">
-        <v>手语歌讲义</v>
-      </c>
-      <c r="C6" s="9" t="n">
+      <c r="B6" s="4" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C6" s="8" t="n">
         <v>46006</v>
       </c>
-      <c r="D6" s="8" t="str">
+      <c r="D6" s="4" t="str">
         <v>大鱼</v>
       </c>
-      <c r="E6" s="8" t="str"/>
-      <c r="F6" s="9" t="str"/>
-      <c r="G6" s="8" t="str">
+      <c r="E6" s="4" t="str"/>
+      <c r="F6" s="8" t="str"/>
+      <c r="G6" s="4" t="str">
         <v>日期为已确认授课日</v>
       </c>
-      <c r="H6" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="8" t="str">
+      <c r="H6" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="5" t="str">
         <v>《暮色回响》手语讲义定稿（已校）.docx</v>
       </c>
-      <c r="B7" s="8" t="str">
+      <c r="B7" s="5" t="str">
         <v>手语歌讲义</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>46007</v>
       </c>
-      <c r="D7" s="8" t="str">
+      <c r="D7" s="5" t="str">
         <v>树林、菠萝</v>
       </c>
-      <c r="E7" s="8" t="str"/>
+      <c r="E7" s="5" t="str"/>
       <c r="F7" s="9" t="str"/>
-      <c r="G7" s="8" t="str">
+      <c r="G7" s="5" t="str">
         <v>日期为已确认授课日</v>
       </c>
-      <c r="H7" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="8" t="str">
+      <c r="H7" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="4" t="str">
         <v>26春高新第一次手语小班.pdf</v>
       </c>
-      <c r="B8" s="8" t="str">
+      <c r="B8" s="4" t="str">
         <v>小班讲义</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>46082</v>
       </c>
-      <c r="D8" s="8" t="str">
+      <c r="D8" s="4" t="str">
         <v>二萌</v>
       </c>
-      <c r="E8" s="8" t="str"/>
-      <c r="F8" s="9" t="str"/>
-      <c r="G8" s="8" t="str">
+      <c r="E8" s="4" t="str"/>
+      <c r="F8" s="8" t="str"/>
+      <c r="G8" s="4" t="str">
         <v>日期为已确认授课日</v>
       </c>
-      <c r="H8" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="8" t="str">
+      <c r="H8" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="5" t="str">
         <v>26春本部第一次手语小班.pdf</v>
       </c>
-      <c r="B9" s="8" t="str">
+      <c r="B9" s="5" t="str">
         <v>小班讲义</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>46088</v>
       </c>
-      <c r="D9" s="8" t="str">
+      <c r="D9" s="5" t="str">
         <v>二萌</v>
       </c>
-      <c r="E9" s="8" t="str"/>
+      <c r="E9" s="5" t="str"/>
       <c r="F9" s="9" t="str"/>
-      <c r="G9" s="8" t="str">
+      <c r="G9" s="5" t="str">
         <v>日期为已确认授课日</v>
       </c>
-      <c r="H9" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="8" t="str">
+      <c r="H9" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="4" t="str">
         <v>我喜欢Ver1editby二萌.pdf</v>
       </c>
-      <c r="B10" s="8" t="str">
-        <v>手语歌讲义</v>
-      </c>
-      <c r="C10" s="9" t="n">
+      <c r="B10" s="4" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>46102</v>
       </c>
-      <c r="D10" s="8" t="str">
+      <c r="D10" s="4" t="str">
         <v>二萌</v>
       </c>
-      <c r="E10" s="8" t="str"/>
-      <c r="F10" s="9" t="str"/>
-      <c r="G10" s="8" t="str">
+      <c r="E10" s="4" t="str"/>
+      <c r="F10" s="8" t="str"/>
+      <c r="G10" s="4" t="str">
         <v>日期据讲义署名</v>
       </c>
-      <c r="H10" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="8" t="str">
+      <c r="H10" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="5" t="str">
         <v>太阳升起的舞蹈_讲义版_B版.docx</v>
       </c>
-      <c r="B11" s="8" t="str">
+      <c r="B11" s="5" t="str">
         <v>讲义打印稿</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>46312</v>
       </c>
-      <c r="D11" s="8" t="str">
+      <c r="D11" s="5" t="str">
         <v>联星、回忆</v>
       </c>
-      <c r="E11" s="8" t="str">
+      <c r="E11" s="5" t="str">
         <v>二萌</v>
       </c>
       <c r="F11" s="9" t="str"/>
-      <c r="G11" s="8" t="str">
+      <c r="G11" s="5" t="str">
         <v>讲义标注日期；当前B版</v>
       </c>
-      <c r="H11" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="8" t="str">
+      <c r="H11" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="4" t="str">
         <v>Manual de lenguaje de señas peruanas.pdf</v>
       </c>
-      <c r="B12" s="8" t="str">
+      <c r="B12" s="4" t="str">
         <v>特殊语言词典</v>
       </c>
-      <c r="C12" s="9" t="str"/>
-      <c r="D12" s="8" t="str"/>
-      <c r="E12" s="8" t="str"/>
-      <c r="F12" s="9" t="str"/>
-      <c r="G12" s="8" t="str">
+      <c r="C12" s="8" t="str"/>
+      <c r="D12" s="4" t="str"/>
+      <c r="E12" s="4" t="str"/>
+      <c r="F12" s="8" t="str"/>
+      <c r="G12" s="4" t="str">
         <v>秘鲁手语参考手册</v>
       </c>
-      <c r="H12" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="8" t="str">
+      <c r="H12" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="5" t="str">
         <v>RE太阳升起的舞蹈_教学整理版_四修.docx</v>
       </c>
-      <c r="B13" s="8" t="str">
+      <c r="B13" s="5" t="str">
         <v>讲义修改稿</v>
       </c>
       <c r="C13" s="9" t="str"/>
-      <c r="D13" s="8" t="str"/>
-      <c r="E13" s="8" t="str"/>
+      <c r="D13" s="5" t="str"/>
+      <c r="E13" s="5" t="str"/>
       <c r="F13" s="9" t="str"/>
-      <c r="G13" s="8" t="str">
+      <c r="G13" s="5" t="str">
         <v>四修组长批阅，保留原生批注</v>
       </c>
-      <c r="H13" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="8" t="str">
+      <c r="H13" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="4" t="str">
         <v>太阳升起的舞蹈_手语翻译_拓宽版.docx</v>
       </c>
-      <c r="B14" s="8" t="str">
-        <v>讲义修改稿</v>
-      </c>
-      <c r="C14" s="9" t="str"/>
-      <c r="D14" s="8" t="str"/>
-      <c r="E14" s="8" t="str"/>
-      <c r="F14" s="9" t="str"/>
-      <c r="G14" s="8" t="str">
+      <c r="B14" s="4" t="str">
+        <v>讲义修改稿</v>
+      </c>
+      <c r="C14" s="8" t="str"/>
+      <c r="D14" s="4" t="str"/>
+      <c r="E14" s="4" t="str"/>
+      <c r="F14" s="8" t="str"/>
+      <c r="G14" s="4" t="str">
         <v>早期智能体稿，含协作批注</v>
       </c>
-      <c r="H14" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="8" t="str">
+      <c r="H14" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="5" t="str">
         <v>太阳升起的舞蹈_手语翻译_纯译版.docx</v>
       </c>
-      <c r="B15" s="8" t="str">
+      <c r="B15" s="5" t="str">
         <v>讲义修改稿</v>
       </c>
       <c r="C15" s="9" t="str"/>
-      <c r="D15" s="8" t="str"/>
-      <c r="E15" s="8" t="str"/>
+      <c r="D15" s="5" t="str"/>
+      <c r="E15" s="5" t="str"/>
       <c r="F15" s="9" t="str"/>
-      <c r="G15" s="8" t="str">
+      <c r="G15" s="5" t="str">
         <v>早期智能体稿，含协作批注</v>
       </c>
-      <c r="H15" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="8" t="str">
+      <c r="H15" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="4" t="str">
         <v>太阳升起的舞蹈_教学整理版_三修.docx</v>
       </c>
-      <c r="B16" s="8" t="str">
-        <v>讲义修改稿</v>
-      </c>
-      <c r="C16" s="9" t="str"/>
-      <c r="D16" s="8" t="str"/>
-      <c r="E16" s="8" t="str"/>
-      <c r="F16" s="9" t="str"/>
-      <c r="G16" s="8" t="str">
+      <c r="B16" s="4" t="str">
+        <v>讲义修改稿</v>
+      </c>
+      <c r="C16" s="8" t="str"/>
+      <c r="D16" s="4" t="str"/>
+      <c r="E16" s="4" t="str"/>
+      <c r="F16" s="8" t="str"/>
+      <c r="G16" s="4" t="str">
         <v>制作过程稿</v>
       </c>
-      <c r="H16" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="8" t="str">
+      <c r="H16" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="5" t="str">
         <v>太阳升起的舞蹈_教学整理版_二修.docx</v>
       </c>
-      <c r="B17" s="8" t="str">
+      <c r="B17" s="5" t="str">
         <v>讲义修改稿</v>
       </c>
       <c r="C17" s="9" t="str"/>
-      <c r="D17" s="8" t="str"/>
-      <c r="E17" s="8" t="str"/>
+      <c r="D17" s="5" t="str"/>
+      <c r="E17" s="5" t="str"/>
       <c r="F17" s="9" t="str"/>
-      <c r="G17" s="8" t="str">
+      <c r="G17" s="5" t="str">
         <v>制作过程稿</v>
       </c>
-      <c r="H17" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="8" t="str">
+      <c r="H17" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="4" t="str">
         <v>太阳升起的舞蹈_教学整理版_修订.docx</v>
       </c>
-      <c r="B18" s="8" t="str">
-        <v>讲义修改稿</v>
-      </c>
-      <c r="C18" s="9" t="str"/>
-      <c r="D18" s="8" t="str"/>
-      <c r="E18" s="8" t="str"/>
-      <c r="F18" s="9" t="str"/>
-      <c r="G18" s="8" t="str">
+      <c r="B18" s="4" t="str">
+        <v>讲义修改稿</v>
+      </c>
+      <c r="C18" s="8" t="str"/>
+      <c r="D18" s="4" t="str"/>
+      <c r="E18" s="4" t="str"/>
+      <c r="F18" s="8" t="str"/>
+      <c r="G18" s="4" t="str">
         <v>制作过程稿</v>
       </c>
-      <c r="H18" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="8" t="str">
+      <c r="H18" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="5" t="str">
         <v>太阳升起的舞蹈_教学整理版_四修.docx</v>
       </c>
-      <c r="B19" s="8" t="str">
+      <c r="B19" s="5" t="str">
         <v>讲义修改稿</v>
       </c>
       <c r="C19" s="9" t="str"/>
-      <c r="D19" s="8" t="str"/>
-      <c r="E19" s="8" t="str"/>
+      <c r="D19" s="5" t="str"/>
+      <c r="E19" s="5" t="str"/>
       <c r="F19" s="9" t="str"/>
-      <c r="G19" s="8" t="str">
+      <c r="G19" s="5" t="str">
         <v>制作过程稿</v>
       </c>
-      <c r="H19" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="8" t="str">
+      <c r="H19" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="4" t="str">
         <v>太阳升起的舞蹈_教学整理版_贴图工作稿.docx</v>
       </c>
-      <c r="B20" s="8" t="str">
-        <v>讲义修改稿</v>
-      </c>
-      <c r="C20" s="9" t="str"/>
-      <c r="D20" s="8" t="str"/>
-      <c r="E20" s="8" t="str"/>
-      <c r="F20" s="9" t="str"/>
-      <c r="G20" s="8" t="str">
+      <c r="B20" s="4" t="str">
+        <v>讲义修改稿</v>
+      </c>
+      <c r="C20" s="8" t="str"/>
+      <c r="D20" s="4" t="str"/>
+      <c r="E20" s="4" t="str"/>
+      <c r="F20" s="8" t="str"/>
+      <c r="G20" s="4" t="str">
         <v>制作过程稿</v>
       </c>
-      <c r="H20" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="8" t="str">
+      <c r="H20" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="5" t="str">
         <v>太阳升起的舞蹈_老师注释版_二萌修后_A版.docx</v>
       </c>
-      <c r="B21" s="8" t="str">
+      <c r="B21" s="5" t="str">
         <v>讲义修改稿</v>
       </c>
       <c r="C21" s="9" t="str"/>
-      <c r="D21" s="8" t="str"/>
-      <c r="E21" s="8" t="str"/>
+      <c r="D21" s="5" t="str"/>
+      <c r="E21" s="5" t="str"/>
       <c r="F21" s="9" t="str"/>
-      <c r="G21" s="8" t="str">
+      <c r="G21" s="5" t="str">
         <v>教师备注稿；当前主要参照为B版</v>
       </c>
-      <c r="H21" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="8" t="str">
+      <c r="H21" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="4" t="str">
         <v>太阳升起的舞蹈_老师注释版_组长修后_B版.docx</v>
       </c>
-      <c r="B22" s="8" t="str">
-        <v>讲义修改稿</v>
-      </c>
-      <c r="C22" s="9" t="str"/>
-      <c r="D22" s="8" t="str"/>
-      <c r="E22" s="8" t="str"/>
-      <c r="F22" s="9" t="str"/>
-      <c r="G22" s="8" t="str">
+      <c r="B22" s="4" t="str">
+        <v>讲义修改稿</v>
+      </c>
+      <c r="C22" s="8" t="str"/>
+      <c r="D22" s="4" t="str"/>
+      <c r="E22" s="4" t="str"/>
+      <c r="F22" s="8" t="str"/>
+      <c r="G22" s="4" t="str">
         <v>教师备注稿；当前主要参照为B版</v>
       </c>
-      <c r="H22" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="8" t="str">
+      <c r="H22" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="5" t="str">
         <v>太阳升起的舞蹈_讲义版_A版.docx</v>
       </c>
-      <c r="B23" s="8" t="str">
+      <c r="B23" s="5" t="str">
         <v>讲义打印稿</v>
       </c>
       <c r="C23" s="9" t="str"/>
-      <c r="D23" s="8" t="str"/>
-      <c r="E23" s="8" t="str"/>
+      <c r="D23" s="5" t="str"/>
+      <c r="E23" s="5" t="str"/>
       <c r="F23" s="9" t="str"/>
-      <c r="G23" s="8" t="str">
+      <c r="G23" s="5" t="str">
         <v>打印稿；当前主要参照为B版</v>
       </c>
-      <c r="H23" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="8" t="str">
+      <c r="H23" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="4" t="str">
         <v>输出目录_太阳升起的舞蹈_手语翻译_拓宽版.docx</v>
       </c>
-      <c r="B24" s="8" t="str">
-        <v>讲义修改稿</v>
-      </c>
-      <c r="C24" s="9" t="str"/>
-      <c r="D24" s="8" t="str"/>
-      <c r="E24" s="8" t="str"/>
-      <c r="F24" s="9" t="str"/>
-      <c r="G24" s="8" t="str">
+      <c r="B24" s="4" t="str">
+        <v>讲义修改稿</v>
+      </c>
+      <c r="C24" s="8" t="str"/>
+      <c r="D24" s="4" t="str"/>
+      <c r="E24" s="4" t="str"/>
+      <c r="F24" s="8" t="str"/>
+      <c r="G24" s="4" t="str">
         <v>早期智能体稿，含协作批注</v>
       </c>
-      <c r="H24" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="8" t="str">
+      <c r="H24" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="5" t="str">
         <v>输出目录_太阳升起的舞蹈_手语翻译_纯译版.docx</v>
       </c>
-      <c r="B25" s="8" t="str">
+      <c r="B25" s="5" t="str">
         <v>讲义修改稿</v>
       </c>
       <c r="C25" s="9" t="str"/>
-      <c r="D25" s="8" t="str"/>
-      <c r="E25" s="8" t="str"/>
+      <c r="D25" s="5" t="str"/>
+      <c r="E25" s="5" t="str"/>
       <c r="F25" s="9" t="str"/>
-      <c r="G25" s="8" t="str">
+      <c r="G25" s="5" t="str">
         <v>早期智能体稿，含协作批注</v>
       </c>
-      <c r="H25" s="8" t="str">
-        <v>查看</v>
-      </c>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="8" t="str">
+      <c r="H25" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="4" t="str">
         <v>手语基础教程（第二版）.pdf</v>
       </c>
-      <c r="B26" s="8" t="str">
+      <c r="B26" s="4" t="str">
         <v>教材</v>
       </c>
-      <c r="C26" s="9" t="str"/>
-      <c r="D26" s="8" t="str">
+      <c r="C26" s="8" t="str"/>
+      <c r="D26" s="4" t="str">
         <v>郑璇；整理宫星</v>
       </c>
-      <c r="E26" s="8" t="str"/>
-      <c r="F26" s="9" t="str"/>
-      <c r="G26" s="8" t="str">
+      <c r="E26" s="4" t="str"/>
+      <c r="F26" s="8" t="str"/>
+      <c r="G26" s="4" t="str">
         <v>提供文本标注2025第二版；具体日期未提供</v>
       </c>
-      <c r="H26" s="8" t="str">
+      <c r="H26" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="5" t="str">
+        <v>Two Oruguitas</v>
+      </c>
+      <c r="B27" s="5" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C27" s="9" t="str"/>
+      <c r="D27" s="5" t="str">
+        <v>联星&amp;八月</v>
+      </c>
+      <c r="E27" s="5" t="str"/>
+      <c r="F27" s="9" t="str"/>
+      <c r="G27" s="5" t="str">
+        <v>带批注讲义；原文署名2026.4.11</v>
+      </c>
+      <c r="H27" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="4" t="str">
+        <v>小美满</v>
+      </c>
+      <c r="B28" s="4" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C28" s="8" t="str"/>
+      <c r="D28" s="4" t="str">
+        <v>西柚&amp;彩云</v>
+      </c>
+      <c r="E28" s="4" t="str"/>
+      <c r="F28" s="8" t="str"/>
+      <c r="G28" s="4" t="str">
+        <v>3.0ver，带批注；原文署名2025.3.22；两稿并存</v>
+      </c>
+      <c r="H28" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="5" t="str">
+        <v>小美满</v>
+      </c>
+      <c r="B29" s="5" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C29" s="9" t="str"/>
+      <c r="D29" s="5" t="str">
+        <v>西柚&amp;彩云</v>
+      </c>
+      <c r="E29" s="5" t="str"/>
+      <c r="F29" s="9" t="str"/>
+      <c r="G29" s="5" t="str">
+        <v>3.0ver，带批注；原文署名2025.3.22；两稿并存</v>
+      </c>
+      <c r="H29" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="4" t="str">
+        <v>暮色回响</v>
+      </c>
+      <c r="B30" s="4" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C30" s="8" t="str"/>
+      <c r="D30" s="4" t="str"/>
+      <c r="E30" s="4" t="str"/>
+      <c r="F30" s="8" t="str"/>
+      <c r="G30" s="4" t="str">
+        <v>初稿（改）2.0，带批注；与已有定稿并存</v>
+      </c>
+      <c r="H30" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="5" t="str">
+        <v>Two Oruguitas（终稿）</v>
+      </c>
+      <c r="B31" s="5" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C31" s="9" t="str"/>
+      <c r="D31" s="5" t="str">
+        <v>联星&amp;八月</v>
+      </c>
+      <c r="E31" s="5" t="str"/>
+      <c r="F31" s="9" t="str"/>
+      <c r="G31" s="5" t="str">
+        <v>终稿PDF，6页；正文署名2026.4.11；不以文件修改时间判定授课日期</v>
+      </c>
+      <c r="H31" s="5" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="4" t="str">
+        <v>Two Oruguitas（三改）</v>
+      </c>
+      <c r="B32" s="4" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C32" s="8" t="str"/>
+      <c r="D32" s="4" t="str">
+        <v>联星&amp;八月</v>
+      </c>
+      <c r="E32" s="4" t="str"/>
+      <c r="F32" s="8" t="str"/>
+      <c r="G32" s="4" t="str">
+        <v>三改PDF，6页；正文署名2026.4.11；不以文件修改时间判定授课日期</v>
+      </c>
+      <c r="H32" s="4" t="str">
+        <v>查看</v>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="5" t="str">
+        <v>Two Oruguitas（二改）</v>
+      </c>
+      <c r="B33" s="5" t="str">
+        <v>手语歌讲义</v>
+      </c>
+      <c r="C33" s="9" t="str"/>
+      <c r="D33" s="5" t="str">
+        <v>联星&amp;八月</v>
+      </c>
+      <c r="E33" s="5" t="str"/>
+      <c r="F33" s="9" t="str"/>
+      <c r="G33" s="5" t="str">
+        <v>二改PDF，6页；正文署名2026.4.11；不以文件修改时间判定授课日期</v>
+      </c>
+      <c r="H33" s="5" t="str">
         <v>查看</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="link2" ref="H2"/>
-    <hyperlink r:id="link3" ref="H3"/>
-    <hyperlink r:id="link4" ref="H4"/>
-    <hyperlink r:id="link5" ref="H5"/>
-    <hyperlink r:id="link6" ref="H6"/>
-    <hyperlink r:id="link7" ref="H7"/>
-    <hyperlink r:id="link8" ref="H8"/>
-    <hyperlink r:id="link9" ref="H9"/>
-    <hyperlink r:id="link10" ref="H10"/>
-    <hyperlink r:id="link11" ref="H11"/>
-    <hyperlink r:id="link12" ref="H12"/>
-    <hyperlink r:id="link13" ref="H13"/>
-    <hyperlink r:id="link14" ref="H14"/>
-    <hyperlink r:id="link15" ref="H15"/>
-    <hyperlink r:id="link16" ref="H16"/>
-    <hyperlink r:id="link17" ref="H17"/>
-    <hyperlink r:id="link18" ref="H18"/>
-    <hyperlink r:id="link19" ref="H19"/>
-    <hyperlink r:id="link20" ref="H20"/>
-    <hyperlink r:id="link21" ref="H21"/>
-    <hyperlink r:id="link22" ref="H22"/>
-    <hyperlink r:id="link23" ref="H23"/>
-    <hyperlink r:id="link24" ref="H24"/>
-    <hyperlink r:id="link25" ref="H25"/>
-    <hyperlink r:id="link26" ref="H26"/>
+    <hyperlink ref="H2" r:id="source2"/>
+    <hyperlink ref="H3" r:id="source3"/>
+    <hyperlink ref="H4" r:id="source4"/>
+    <hyperlink ref="H5" r:id="source5"/>
+    <hyperlink ref="H6" r:id="source6"/>
+    <hyperlink ref="H7" r:id="source7"/>
+    <hyperlink ref="H8" r:id="source8"/>
+    <hyperlink ref="H9" r:id="source9"/>
+    <hyperlink ref="H10" r:id="source10"/>
+    <hyperlink ref="H11" r:id="source11"/>
+    <hyperlink ref="H12" r:id="source12"/>
+    <hyperlink ref="H13" r:id="source13"/>
+    <hyperlink ref="H14" r:id="source14"/>
+    <hyperlink ref="H15" r:id="source15"/>
+    <hyperlink ref="H16" r:id="source16"/>
+    <hyperlink ref="H17" r:id="source17"/>
+    <hyperlink ref="H18" r:id="source18"/>
+    <hyperlink ref="H19" r:id="source19"/>
+    <hyperlink ref="H20" r:id="source20"/>
+    <hyperlink ref="H21" r:id="source21"/>
+    <hyperlink ref="H22" r:id="source22"/>
+    <hyperlink ref="H23" r:id="source23"/>
+    <hyperlink ref="H24" r:id="source24"/>
+    <hyperlink ref="H25" r:id="source25"/>
+    <hyperlink ref="H26" r:id="source26"/>
+    <hyperlink ref="H27" r:id="source27"/>
+    <hyperlink ref="H28" r:id="source28"/>
+    <hyperlink ref="H29" r:id="source29"/>
+    <hyperlink ref="H30" r:id="source30"/>
+    <hyperlink ref="H31" r:id="source31"/>
+    <hyperlink ref="H32" r:id="source32"/>
+    <hyperlink ref="H33" r:id="source33"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="Rff392738e0824fc7"/>
+    <tablePart r:id="Rc2fe628025674de1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/资料/资料目录.xlsx
+++ b/资料/资料目录.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>授课日期列记录原稿日期</t>
+          <t>授课日期列记录原稿日期；选歌参考：手语课。情感告别题材，以我、你、朋友之间的叙述与对话推进，副歌重复。可参照否定、条件句、情绪表达及人物指向。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -493,7 +493,7 @@
       <c r="F3" s="11" t="str"/>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>讲义标注日期，授课或发布性质待确认</t>
+          <t>讲义标注日期，授课或发布性质待确认；选歌参考：手语课。成长与陪伴题材，海、道路、路口等意象与抽象心境交织，多分句且副歌反复。可参照比喻具体化、句群拆分和重复动作。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -525,7 +525,7 @@
       <c r="F4" s="10" t="str"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>日期据讲义署名</t>
+          <t>日期据讲义署名；选歌参考：手语课。漂泊与故乡题材，第三人称叙事穿插第一人称提问，跨越城市、草原、列车等场景。可参照长修饰句重组、人物视角转换及空间移动。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -557,7 +557,7 @@
       <c r="F5" s="11" t="str"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>日期为已确认授课日</t>
+          <t>日期为已确认授课日；选歌参考：手语课。理想与自由题材，雪、风雨、雾等画面承载心理感受，副歌反复。讲义并列呈现字面与内涵取舍，可参照意象处理、否定疑问和抽象表达。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -589,7 +589,7 @@
       <c r="F6" s="10" t="str"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>日期为已确认授课日</t>
+          <t>日期为已确认授课日；选歌参考：手语课。自由、平等与抗争题材，由人物生命经历转向群体愿望，副歌反复。讲义呈现不同转写方案，可参照象征意象、抽象概念和语义取舍。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -621,7 +621,7 @@
       <c r="F7" s="11" t="str"/>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>日期为已确认授课日</t>
+          <t>日期为已确认授课日；选歌参考：手语课。怀念与离别题材，星、摇椅、落叶、声音等画面连接对逝者的想象，叙述中穿插呼告和疑问。可参照人物回指、动作方向及情绪与场景转换。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="F10" s="10" t="str"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>日期据讲义署名</t>
+          <t>日期据讲义署名；选歌参考：手语课。日常生活与喜爱题材，以“我喜欢”串联季节、场所、人物和物件，句式重复而画面频繁切换。可参照列举、数量、位置关系、类标记及专名指拼。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -753,7 +753,7 @@
       <c r="F11" s="11" t="str"/>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>讲义标注日期；当前B版</t>
+          <t>讲义标注日期；当前B版；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -779,7 +779,7 @@
       <c r="F12" s="10" t="str"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>秘鲁手语参考手册</t>
+          <t>秘鲁手语参考手册；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -805,7 +805,7 @@
       <c r="F13" s="11" t="str"/>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>四修组长批阅，保留原生批注</t>
+          <t>四修组长批阅，保留原生批注；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="F14" s="10" t="str"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>早期智能体稿，含协作批注</t>
+          <t>早期智能体稿，含协作批注；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -857,7 +857,7 @@
       <c r="F15" s="11" t="str"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>早期智能体稿，含协作批注</t>
+          <t>早期智能体稿，含协作批注；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -883,7 +883,7 @@
       <c r="F16" s="10" t="str"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>制作过程稿</t>
+          <t>制作过程稿；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -909,7 +909,7 @@
       <c r="F17" s="11" t="str"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>制作过程稿</t>
+          <t>制作过程稿；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -935,7 +935,7 @@
       <c r="F18" s="10" t="str"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>制作过程稿</t>
+          <t>制作过程稿；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -961,7 +961,7 @@
       <c r="F19" s="11" t="str"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>制作过程稿</t>
+          <t>制作过程稿；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="F20" s="10" t="str"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>制作过程稿</t>
+          <t>制作过程稿；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       <c r="F21" s="11" t="str"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>教师备注稿；当前主要参照为B版</t>
+          <t>教师备注稿；当前主要参照为B版；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1039,7 +1039,7 @@
       <c r="F22" s="10" t="str"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>教师备注稿；当前主要参照为B版</t>
+          <t>教师备注稿；当前主要参照为B版；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="F23" s="11" t="str"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>打印稿；当前主要参照为B版</t>
+          <t>打印稿；当前主要参照为B版；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       <c r="F24" s="10" t="str"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>早期智能体稿，含协作批注</t>
+          <t>早期智能体稿，含协作批注；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1117,7 +1117,7 @@
       <c r="F25" s="11" t="str"/>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>早期智能体稿，含协作批注</t>
+          <t>早期智能体稿，含协作批注；选歌参考：手语课。古文明、祭典与文化交流题材，主歌铺陈文物和场景，过渡含选择疑问，副歌重复并穿插接句。可参照文化词汇、抽象意象具体化及主句与接句组织。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -1177,7 +1177,7 @@
       <c r="F27" s="11" t="str"/>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>带批注讲义；原文署名2026.4.11</t>
+          <t>带批注讲义；原文署名2026.4.11；选歌参考：手语课。以两只毛毛虫化蝶叙述相伴、分离与成长，中英对照并有重复副歌。可参照双主体空间、蛹的内外关系、类标记和成长隐喻；须区分语言版本。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="F28" s="10" t="str"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>最终版本（手语老师确认）；3.0ver；原文署名2025.3.22；选择参照材料时优先使用本稿</t>
+          <t>最终版本（手语老师确认）；3.0ver；原文署名2025.3.22；选择参照材料时优先使用本稿；选歌参考：手语课。日常幸福与自我陪伴题材，路口、云、狗、树叶等具体画面带有拟人和比喻，短句与重复段较多。可参照日常词汇、拟人画面和情绪表达。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1237,7 +1237,7 @@
       <c r="F29" s="11" t="str"/>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>较早版本，供比较修改；最终版本为Re Re Re手语课讲义 小美满 3.0ver.docx</t>
+          <t>较早版本，供比较修改；最终版本为Re Re Re手语课讲义 小美满 3.0ver.docx；选歌参考：手语课。日常幸福与自我陪伴题材，路口、云、狗、树叶等具体画面带有拟人和比喻，短句与重复段较多。可参照日常词汇、拟人画面和情绪表达。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -1263,7 +1263,7 @@
       <c r="F30" s="10" t="str"/>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>初稿（改）2.0，带批注；与已有定稿并存</t>
+          <t>初稿（改）2.0，带批注；与已有定稿并存；选歌参考：手语课。怀念与离别题材，星、摇椅、落叶、声音等画面连接对逝者的想象，叙述中穿插呼告和疑问。可参照人物回指、动作方向及情绪与场景转换。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1293,7 +1293,7 @@
       <c r="F31" s="11" t="str"/>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>终稿PDF，6页；正文署名2026.4.11；不以文件修改时间判定授课日期</t>
+          <t>终稿PDF，6页；正文署名2026.4.11；不以文件修改时间判定授课日期；选歌参考：手语课。以两只毛毛虫化蝶叙述相伴、分离与成长，中英对照并有重复副歌。可参照双主体空间、蛹的内外关系、类标记和成长隐喻；须区分语言版本。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -1323,7 +1323,7 @@
       <c r="F32" s="10" t="str"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>三改PDF，6页；正文署名2026.4.11；不以文件修改时间判定授课日期</t>
+          <t>三改PDF，6页；正文署名2026.4.11；不以文件修改时间判定授课日期；选歌参考：手语课。以两只毛毛虫化蝶叙述相伴、分离与成长，中英对照并有重复副歌。可参照双主体空间、蛹的内外关系、类标记和成长隐喻；须区分语言版本。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1353,7 +1353,7 @@
       <c r="F33" s="11" t="str"/>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>二改PDF，6页；正文署名2026.4.11；不以文件修改时间判定授课日期</t>
+          <t>二改PDF，6页；正文署名2026.4.11；不以文件修改时间判定授课日期；选歌参考：手语课。以两只毛毛虫化蝶叙述相伴、分离与成长，中英对照并有重复副歌。可参照双主体空间、蛹的内外关系、类标记和成长隐喻；须区分语言版本。节奏须结合音频核对。</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">

--- a/资料/资料目录.xlsx
+++ b/资料/资料目录.xlsx
@@ -432,7 +432,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="76" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>其实讲义editby二萌.docx</t>
@@ -470,7 +470,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1">
+    <row r="3" ht="76" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>RE永远都会在 讲义 2.0ver (1).docx</t>
@@ -502,7 +502,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
+    <row r="4" ht="76" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>历历万乡.pdf</t>
@@ -534,7 +534,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>海阔天空.docx</t>
@@ -566,7 +566,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="76" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>光辉岁月讲义 (1).docx</t>
@@ -598,7 +598,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="76" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>《暮色回响》手语讲义定稿（已校）.docx</t>
@@ -694,7 +694,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" ht="76" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>我喜欢Ver1editby二萌.pdf</t>
@@ -726,7 +726,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
+    <row r="11" ht="93" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_讲义版_B版.docx</t>
@@ -762,7 +762,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" ht="93" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Manual de lenguaje de señas peruanas.pdf</t>
@@ -788,7 +788,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" ht="93" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>RE太阳升起的舞蹈_教学整理版_四修.docx</t>
@@ -814,7 +814,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
+    <row r="14" ht="93" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_手语翻译_拓宽版.docx</t>
@@ -840,7 +840,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
+    <row r="15" ht="93" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_手语翻译_纯译版.docx</t>
@@ -866,7 +866,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1">
+    <row r="16" ht="76" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_教学整理版_三修.docx</t>
@@ -892,7 +892,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1">
+    <row r="17" ht="76" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_教学整理版_二修.docx</t>
@@ -918,7 +918,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
+    <row r="18" ht="76" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_教学整理版_修订.docx</t>
@@ -944,7 +944,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="76" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_教学整理版_四修.docx</t>
@@ -970,7 +970,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="76" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_教学整理版_贴图工作稿.docx</t>
@@ -996,7 +996,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="93" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_老师注释版_二萌修后_A版.docx</t>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="93" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_老师注释版_组长修后_B版.docx</t>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="93" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>太阳升起的舞蹈_讲义版_A版.docx</t>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="93" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>输出目录_太阳升起的舞蹈_手语翻译_拓宽版.docx</t>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="93" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>输出目录_太阳升起的舞蹈_手语翻译_纯译版.docx</t>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
+    <row r="27" ht="93" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>RETwo Oruguitas.docx</t>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
+    <row r="28" ht="110" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Re Re Re手语课讲义 小美满 3.0ver.docx</t>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
+    <row r="29" ht="110" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Re Re手语课讲义 小美满 3.0ver.docx</t>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="42" customHeight="1">
+    <row r="30" ht="93" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>RE《暮色回响》手语讲义初稿（改）2.0.docx</t>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="42" customHeight="1">
+    <row r="31" ht="93" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Two Oruguitas - 联星&amp;八月 - 终稿.pdf</t>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="42" customHeight="1">
+    <row r="32" ht="93" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Two Oruguitas - 三改.pdf</t>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="42" customHeight="1">
+    <row r="33" ht="93" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Two Oruguitas - 二改.pdf</t>
